--- a/data/outputs/5. Corporate_Risk_Register (Final).xlsx
+++ b/data/outputs/5. Corporate_Risk_Register (Final).xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Council's ability to cope with a natural disaster.</t>
+          <t>The Council's ability to cope with a natural disaster or malicious/accidental incident that affects civilian support or disrupts existing services.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -518,19 +518,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cmt</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -539,12 +539,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Regularly test Emergency Plan; Test Service Business Continuity Plans; Ensure key emergency planning staff attend regular liaison meetings and training; Update Emergency Management and Rest Plan; Increase and train volunteer rest centre staff; Retain use of Leisure Centres for rest centre sites; Implement on-call officer rota; Complement coordinated Local Resilience Forum and Public Sector response.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>Regularly test the Emergency Plan and Service Business Continuity Plans, and ensure key emergency planning staff attend regular liaison meetings and training.</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,7 +567,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IT system failure risks data security, service disruption, and potential financial or reputational damage.</t>
+          <t>Failure of IT systems leading to data loss, corruption, or inaccuracy, resulting in service disruption, security breaches, financial penalties, and reputational damage.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -574,28 +582,36 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Carol Pilson / Peter Catchpole</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>- Effective auditing of systems and data held. - Data backed-up securely off-site. - Regular penetration testing. - Regular review of business continuity plans - Disaster Recovery testing is undertaken at regular intervals</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>Implement and regularly test data protection policies, system security measures, business continuity plans, and disaster recovery protocols.</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -610,7 +626,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Breach of ICT security causing service loss and potential financial or reputational damage.</t>
+          <t>Breach of ICT security causes loss of service due to hardware failure or electronic attack, leading to service disruption, security breaches, financial penalties, and reputational damage.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -625,28 +641,36 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Peter Catchpole</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Effective auditing of systems and data; secure off-site data backups; regular penetration testing; use of anti-virus software, geographically distributed servers, tested disaster recovery plans, off-site backups, secondary power supply, revised security policies, and business continuity plans with manual operation; subscription to NCSC Web Check service; regular software updates.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>Implement and maintain anti-virus software, geographically distributed servers, tested disaster recovery plans, off-site backups, secondary power supply, revised security policies, and business continuity plans for critical services.</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -661,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Political changes in national priorities may require additional resources and conflict with local consultation outcomes.</t>
+          <t>Changes in national political priorities may require immediate, resource-intensive changes that conflict with established community consultation priorities.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -676,14 +700,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paul Medd</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -692,12 +716,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Understanding and acting on intelligence from LGA, CIPFA and other local government sources. Resources identified, approved and implemented without delay. Constant monitoring. Horizon scanning via professional bodies. Joint/collaborative working.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>Monitor intelligence from professional bodies like the LGA and CIPFA, and implement approved resources without delay to respond to policy changes.</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -712,12 +744,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contractor or supplier failure may lead to service delivery shortfalls and increased costs.</t>
+          <t>Failure of contractors and suppliers working on the Council’s behalf to deliver services or meet agreed performance objectives, leading to additional costs or failed objectives.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -727,14 +759,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Ship Documented - Service Level Agreements - Contract Monitoring - Trained/Skilled Staff - Project Management - Relationship Management - Business Continuity Plans</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -743,12 +775,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Regular contract monitoring, robust contracts with risk registers, financial checks, contingency plans, and dedicated contract management.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>Implement robust procurement processes, create strong contracts, document accountability, establish Service Level Agreements, and conduct regular contract monitoring and performance reviews.</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -763,7 +803,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A major health and safety incident could lead to costly inquiries, service disruption, and prosecution.</t>
+          <t>Major health and safety incident at Council leads to costs for inquiry, disruption to service and possible prosecution.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -773,19 +813,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cmt</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -794,12 +834,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>- Ensure health and safety is standard agenda on all team meetings. - Ensure equipment inventory and inspections are up to date. - Review Risk Assessments and Action Plans. - Capture Port near misses and asses learning points</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>Ensure health and safety is standard agenda on all team meetings and maintain up-to-date equipment inventory and inspections.</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -814,7 +862,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Service provision and performance may be affected by organisational change, industrial action, or staff sickness, leading to complaints, poor performance, and additional costs.</t>
+          <t>Service provision and performance are affected by organisational change, industrial action, or staff sickness, leading to complaints, poor performance, and potential additional costs.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,11 +877,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Peter Catchpole</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -845,12 +893,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Business continuity plans, workforce planning, health surveillance, mental health and stress support, staff engagement, and comprehensive health and wellbeing programme.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>Maintain and regularly test business continuity plans, implement workforce planning, and support staff health and wellbeing programs.</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -865,12 +921,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Legislative changes may require significant organizational adaptation and risk GDPR non-compliance.</t>
+          <t>Legislative changes from Central Government or EU requiring significant organizational alteration, including welfare reform, devolution, new burdens, and GDPR breach risks.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -880,11 +936,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carol Pilson</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -896,12 +952,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Monitoring Officer horizon scanning, service manager responsibilities, financial and workforce planning, professional body membership, change management, detailed project plans, consultation responses, intelligence use, staff training, procedure updates, professional networking, best practice adoption, and dedicated GDPR roles and training.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>Implement horizon scanning, staff training, professional networking, and respond to government consultations to proactively manage legislative changes and ensure GDPR compliance.</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,12 +980,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brexit-related legislative, funding, and policy changes may adversely affect Council services.</t>
+          <t>Brexit-related uncertainty and potential legislative, funding, and policy changes may adversely affect the Council's ability to provide services.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -931,28 +995,36 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Peter Catchpole / Carol Pilson</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Horizon scanning, financial and workforce planning, membership in professional bodies, management of change approach, detailed project plans, monitoring intelligence, identifying policy changes, active participation in Brexit project groups and forums, workforce review, and community awareness promotion.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>Conduct horizon scanning, financial and workforce planning, and manage change through detailed project plans to implement necessary adjustments.</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -967,7 +1039,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Funding changes threaten the Council's financial sustainability.</t>
+          <t>Changes to government funding systems and economic conditions could make the Council financially unsustainable.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -982,14 +1054,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Peter Catchpole</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -998,12 +1070,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Using intelligence to model and plan for future changes and risks and move away from reliance on Govt funding to balance our budget. Regular monitoring of current position and reporting to Members. Workforce planning covers all scenarios. Inclusion in national working groups, modelling and lobbying for funding system after RSG ceases. Sharing Council’s Efficiency Plan with the Government allows guaranteed multi-year grant settlement raising funding certainty. Shared services and partnership working</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+          <t>Implement and monitor the Commercialisation and Investment Strategy, while actively participating in national working groups to lobby for a stable future funding system.</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1018,12 +1098,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fraud and error against the Council risk financial loss, reputational harm, and additional costs.</t>
+          <t>Fraud and error committed against the Council by internal or external threats, leading to financial loss, reputational harm, and additional costs.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1033,28 +1113,36 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Peter Catchpole / Carol Pilson</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Increase staff vigilance, fraud awareness training for managers, raise profile of successful prosecutions.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+          <t>Implement and enforce anti-fraud policies, conduct regular fraud risk assessments, and provide ongoing fraud awareness training for all staff.</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1069,7 +1157,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Failure of governance in major partners or the Council due to partnership working.</t>
+          <t>Failure of governance in major partners or the Council due to partnership working, leading to unachieved priorities and poor performance.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1079,16 +1167,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carol Pilson / Peter Catchpole</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>8</v>
@@ -1100,12 +1188,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Assurance that governance models are correctly followed and in the Council’s interests; support Members in governance of partnership bodies; Internal Audit partnership arrangements; ensure the Council’s interests are protected as Members of the Combined Authority and as Officers working on joint projects; ensure all Partners have robust Business Continuity Plans in place; GDPR compliance; robust ICT governance processes.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+          <t>Ensure governance models are correctly followed, support Members in partnership governance, and conduct internal audits of partnership arrangements.</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1120,7 +1216,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Failure to achieve savings targets risks budget deficits and inability to set a balanced budget.</t>
+          <t>Failure to achieve required savings targets results in greater than budgeted costs and potential risk of Council not being able to set a balanced budget.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1135,28 +1231,36 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cmt</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Implement robust budget and performance monitoring, service transformation projects, and a commercialisation strategy to control costs and increase income streams.</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
         <v>7</v>
       </c>
-      <c r="H14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>- Heightened analysis of budgets and services by CMT - Implement Service Transformation - Implement Procurement Strategy - Corporate plan - Pursue action to increase income streams - Performance Management Framework - Budget and performance monitoring - Robust Workforce planning - Project Management processes</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1171,12 +1275,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Capital funding strategy failure risks financial shortfalls and increased burden on the Council.</t>
+          <t>Capital funding strategy failure leading to financial shortfalls and increased burden on the Council.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1186,14 +1290,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Peter Catchpole</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1202,12 +1306,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Asset Management Plan, disposal strategy, regular monitoring, Cabinet review, pursuit of additional funding, project-level valuation monitoring, market-aligned planning, and partner consultation.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+          <t>Implement asset management plan, disposal strategy, and regular high-level monitoring of capital receipts and funding opportunities.</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1222,12 +1334,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poor communication with stakeholders and staff leads to misdirected resources and lack of support for change.</t>
+          <t>Poor communication with stakeholders and staff leads to poorly informed direction of resources and lack of support for change.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1237,7 +1349,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carol Pilson</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1253,12 +1365,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Internal and external publications, staff meetings, stakeholder networks, press releases, CSE accreditation, consultation strategy, MTSP group, CSE Action Plan, staff survey, public consultations, 3cs training, team meetings, Chief Executive updates.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+          <t>Implement regular internal/external publications, staff meetings, stakeholder networks, and coordinated communication programs.</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1273,7 +1393,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Commercial uncertainties in the Council's investment strategy risk reputational damage, financial loss, and service impacts.</t>
+          <t>Commercial uncertainties associated with decisions taken as part of the Council's Commercial and Investment Strategy.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1288,11 +1408,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cmt</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>8</v>
@@ -1304,12 +1424,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Robust oversight and governance arrangements, expert professional advice, robust budget management, thorough project management and business cases process.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+          <t>Implement robust oversight, governance arrangements, and expert professional advice to manage commercial uncertainties.</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1324,12 +1452,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Failure of external investment institutions affecting funds and cash flow.</t>
+          <t>Failure of external investment institutions affecting availability of funds or return on investment, reducing cash flow and resource availability.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1339,11 +1467,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Peter Catchpole</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
         <v>8</v>
@@ -1355,12 +1483,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>- Effective Treasury Management strategy. - Robust auditing of processes and policies.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+          <t>Implement and maintain an effective Treasury Management strategy with robust auditing of processes and policies.</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1375,7 +1511,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Insufficient staff and leadership capacity risk service delivery and legal challenges.</t>
+          <t>Insufficient staff and leadership capacity to deliver Council services and priorities, leading to poor service standards, disruption, and potential legal challenges.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1390,11 +1526,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cmt</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
         <v>8</v>
@@ -1406,12 +1542,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>- Learning &amp; Development framework / Training - Working environment /culture - Staff Committee - MTSP - Flexible working - Established suite of people policies &amp; Procedures - Business continuity plans - Management training - 121s /Springboard staff development and appraisals - Service planning process - Access to interim staff via frameworks - Effective sickness management - Effective Governance structures - Ensure all services have effective Workforce plans incorporated into Service Plans, which ensure all work is prioritised - Effective succession planning. - Effective use of project management approaches/ principles when delivering priorities/ strategies</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+          <t>Ensure all services have effective Workforce Plans incorporated into Service Plans and implement effective succession planning.</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1426,7 +1570,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lack of access to Council premises disrupts service delivery.</t>
+          <t>Lack of access to Council premises prevents services from being delivered, causing service disruption.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,19 +1580,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Peter Catchpole</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1457,12 +1601,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Regularly test Emergency Plan, Test service Business Continuity Plans, Ensure key emergency planning staff attend regular liaison meetings and training, Provision of 'drop down' facilities for staff</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+          <t>Regularly test and update business continuity and emergency plans, including remote working capabilities.</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1477,12 +1629,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Overruns in major Council projects on time or cost, leading to reputational damage.</t>
+          <t>Over-run of major Council projects in time or cost leading to failure to achieve project aims and reputational damage.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1492,14 +1644,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Cmt</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1508,12 +1660,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Robust project management, effective risk registers, and oversight by CMT and Cabinet.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>Implement robust project management methodology and maintain effective risk registers for all projects.</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1528,12 +1688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Legislative changes.</t>
+          <t>Legislative changes could impact project compliance and viability.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1543,28 +1703,36 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Monitor regulatory updates and engage legal counsel to assess impacts on project plans.</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
         <v>5</v>
       </c>
-      <c r="H22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Implement legislative monitoring and advocacy program</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1579,43 +1747,51 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brexit-related risks.</t>
+          <t>Brexit-related uncertainties affecting project operations and compliance.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Brexit</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+          <t>Monitor Brexit developments and update project compliance plans accordingly.</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>5</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1630,12 +1806,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Failure of contractors and suppliers working on the Council’s behalf.</t>
+          <t>Contractors and suppliers working on the Council’s behalf may fail to deliver.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1645,11 +1821,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
         <v>7</v>
@@ -1661,12 +1837,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Implement robust contract management, due diligence, and contingency planning.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+          <t>The Project Manager must implement robust contract monitoring and enforce service level agreements.</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1696,14 +1880,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Lead engineer</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1712,12 +1896,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Implement robust IT disaster recovery and business continuity plans.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+          <t>Implement and regularly test system redundancy and data backup procedures.</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1747,14 +1939,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1763,12 +1955,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Implement recruitment and retention strategies, including flexible working and competitive pay.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+          <t>Develop and implement a recruitment and retention strategy to ensure adequate staffing levels.</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1783,7 +1983,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Breach of ICT security causing loss of service.</t>
+          <t>A breach of ICT security causes loss of service.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1798,14 +1998,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Lead engineer</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1814,12 +2014,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Implement multi-factor authentication, regular security audits, and employee cybersecurity training.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+          <t>Implement enhanced cybersecurity protocols and regular security audits.</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1834,7 +2042,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lack of access to Council premises prevents service delivery.</t>
+          <t>Lack of access to Council premises prevents services from being delivered.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1849,14 +2057,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1865,12 +2073,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Implement remote work protocols and alternative service delivery channels.</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+          <t>Develop and implement a robust business continuity plan with remote service delivery options.</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1885,7 +2101,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Funding changes threaten the Council's sustainability.</t>
+          <t>Changes in funding could render the Council financially unsustainable.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1900,14 +2116,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1916,12 +2132,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Implement financial sustainability plan, diversify revenue streams, and conduct regular financial health reviews.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+          <t>Develop and maintain a diversified funding strategy and robust financial contingency plans.</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1936,7 +2160,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The Council's ability to cope with a natural disaster.</t>
+          <t>The Council's ability to cope with a natural disaster is insufficient.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1946,33 +2170,41 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
         <v>8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>The Council has a Business Continuity Plan and Emergency Plan in place, which are regularly reviewed and tested.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+          <t>Develop and test a comprehensive business continuity and disaster recovery plan.</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1987,43 +2219,51 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Major health and safety incident.</t>
+          <t>A major health and safety incident occurring on the project.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Implement and enforce a comprehensive site safety plan with regular audits and staff training.</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
         <v>8</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Implement comprehensive health and safety training and regular audits.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2038,12 +2278,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fraud and error committed against the Council.</t>
+          <t>Fraud and error are committed against the Council, leading to financial loss and reputational damage.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2053,14 +2293,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2069,12 +2309,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Implement robust financial controls and regular audits.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+          <t>Implement robust financial controls, regular audits, and staff training on fraud prevention and detection procedures.</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2089,12 +2337,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Failure of external investment institutions.</t>
+          <t>Failure of external investment institutions could disrupt project funding.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2104,14 +2352,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2120,12 +2368,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Diversify investment portfolio across multiple institutions and asset classes.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+          <t>Diversify funding sources and conduct regular financial health checks on investment partners.</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2145,24 +2401,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2171,12 +2427,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Strengthen partnership agreements and oversight mechanisms.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+          <t>Establish and regularly review clear governance frameworks and communication protocols with all partners.</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>6</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2206,14 +2470,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2222,12 +2486,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Implement cost-saving initiatives and monitor financial performance.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+          <t>Implement strict budget monitoring and regular financial reviews to track savings progress.</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2242,12 +2514,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Over-run of major Council projects in time or cost.</t>
+          <t>Major Council projects may over-run in time or cost.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2261,10 +2533,10 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2273,12 +2545,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Implement robust project governance, including clear scope definition, regular progress monitoring, and contingency planning.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+          <t>Implement rigorous project monitoring, milestone tracking, and contingency planning.</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2293,7 +2573,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Service provision may be affected by organisational change.</t>
+          <t>Service provision is affected by organisational change.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2308,28 +2588,36 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Develop and implement a business continuity plan to maintain service levels during organisational transitions.</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="n">
         <v>5</v>
       </c>
-      <c r="H37" t="n">
-        <v>6</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Implement change management framework with staff engagement and service continuity planning.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2344,26 +2632,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Political changes in national priorities.</t>
+          <t>Political changes in national priorities could affect project support or funding.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
         <v>7</v>
@@ -2375,12 +2663,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The risk register should be reviewed and updated to reflect new national priorities, and strategic plans should be aligned accordingly.</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+          <t>Monitor political developments and engage with relevant government bodies to understand and adapt to changing priorities.</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2395,7 +2691,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Capital funding strategy failure.</t>
+          <t>Failure of the capital funding strategy.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2410,28 +2706,36 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
+        <v>9</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Develop and regularly review a robust, diversified funding plan with clear contingency measures.</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
         <v>7</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Implement a multi-year capital funding strategy with regular reviews and stakeholder engagement.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2451,7 +2755,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2461,14 +2765,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2477,12 +2781,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Implement a structured stakeholder engagement plan with regular updates and feedback mechanisms.</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+          <t>Establish and maintain a formal stakeholder communication plan with regular updates.</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2497,7 +2809,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Failure of the Commercialisation &amp; Investment Strategy.</t>
+          <t>The project faces a risk due to the potential failure of its Commercialisation &amp; Investment Strategy.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2512,14 +2824,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2528,12 +2840,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Implement robust due diligence processes and establish a dedicated oversight committee.</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+          <t>Develop and implement a robust, reviewed commercialisation and investment plan with clear milestones.</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/outputs/5. Corporate_Risk_Register (Final).xlsx
+++ b/data/outputs/5. Corporate_Risk_Register (Final).xlsx
@@ -431,221 +431,221 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Risk ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Project Stage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Project Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Owner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mitigating Action</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Likelihood (1-10) (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Impact (1-10) (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Priority (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Likelihood (1-10) (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Impact (1-10) (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Priority (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Date Added</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Risk ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Project Stage</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Project Category</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Owner</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (1-10) (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (1-10) (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Priority (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigating Action</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (1-10) (post-mitigation)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (1-10) (post-mitigation)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Priority (post-mitigation)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>The Council’s ability to cope with a natural disaster.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Council's ability to cope with a natural disaster or malicious/accidental incident that affects civilian support or disrupts existing services.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cmt</t>
+          <t>Emergency plan, Emergency planning exercises beyond the district, Business continuity plans, Regular exercise and joint public sector workshops for Emergency Planning, Emergency Planning Communications Strategy, Review of approach with partner organisations as a result of lessons learned from ‘near miss’ flood events., Local Resilience Forum</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Regularly test the Emergency Plan and Service Business Continuity Plans, and ensure key emergency planning staff attend regular liaison meetings and training.</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>Failure of IT systems</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Failure of IT systems leading to data loss, corruption, or inaccuracy, resulting in service disruption, security breaches, financial penalties, and reputational damage.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>It Manager</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Carol Pilson / Peter Catchpole</t>
+          <t>Data protection policy and procedure - Freedom of Information publication scheme - Data retention policy and procedure for archive and disposal - Information breach response plan - Monitoring Officer role comprises Senior Information Risk Officer function - Business continuity plans - ICT system security - Public Services Network compliance - Paperless office project - Countywide information sharing framework</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Implement and regularly test data protection policies, system security measures, business continuity plans, and disaster recovery protocols.</t>
-        </is>
+      <c r="J3" t="n">
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>Breach of ICT security causes loss of service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Breach of ICT security causes loss of service due to hardware failure or electronic attack, leading to service disruption, security breaches, financial penalties, and reputational damage.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>It Manager</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Peter Catchpole</t>
+          <t>Anti-virus software, geographically distributed servers, tested disaster recovery plan, back-ups stored off site, secondary power supply, revised security policies, critical services' business continuity plans include manual operation</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -655,646 +655,646 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Implement and maintain anti-virus software, geographically distributed servers, tested disaster recovery plans, off-site backups, secondary power supply, revised security policies, and business continuity plans for critical services.</t>
-        </is>
+      <c r="J4" t="n">
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
         <v>6</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>Political changes in national priorities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Changes in national political priorities may require immediate, resource-intensive changes that conflict with established community consultation priorities.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Regulations</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Uaa Lead</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paul Medd</t>
+          <t>Financial &amp; workforce planning - Monitoring by CMT and resultant Cabinet reports - Clear corporate planning and regular performance monitoring - Effective service &amp; financial planning - Respond to national consultation on key policy changes - Membership of LGA as a Council Outside Body</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Monitor intelligence from professional bodies like the LGA and CIPFA, and implement approved resources without delay to respond to policy changes.</t>
-        </is>
+      <c r="J5" t="n">
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Failure of contractors and suppliers working on the Council’s behalf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Failure of contractors and suppliers working on the Council’s behalf to deliver services or meet agreed performance objectives, leading to additional costs or failed objectives.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ship Documented - Service Level Agreements - Contract Monitoring - Trained/Skilled Staff - Project Management - Relationship Management - Business Continuity Plans</t>
+          <t>Procurement processes – including financial aspects/ contract standing orders/ equality standards - Contract process – creation of robust contracts - Accountability and risk ownership documented - Service Level Agreements - Contract monitoring - Trained/skilled staff - Project management - Relationship Management - Business Continuity Plans</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Implement robust procurement processes, create strong contracts, document accountability, establish Service Level Agreements, and conduct regular contract monitoring and performance reviews.</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>Major health and safety incident</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Major health and safety incident at Council leads to costs for inquiry, disruption to service and possible prosecution.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Regulations</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cmt</t>
+          <t>Health &amp; Safety Panel, H&amp;S procedures, audits, training, insurance, robust sickness management</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Ensure health and safety is standard agenda on all team meetings and maintain up-to-date equipment inventory and inspections.</t>
-        </is>
+      <c r="J7" t="n">
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>Service provision affected by organisational change</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Service provision and performance are affected by organisational change, industrial action, or staff sickness, leading to complaints, poor performance, and potential additional costs.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peter Catchpole</t>
+          <t>Working environment / org culture - Staff Committee - Consultation with Staff Side - Flexible working - Established suite of people policies &amp; procedures - Business continuity plans - Management training - “Springboard” appraisal for all staff support and development - CMT monitor and lead on human resource management. - Regular performance monitoring and management - IIP - Access to interim arrangements - Robust sickness absence management - Project management processes</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Maintain and regularly test business continuity plans, implement workforce planning, and support staff health and wellbeing programs.</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Legislative changes requiring significant alteration to organisational capacity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Legislative changes from Central Government or EU requiring significant organizational alteration, including welfare reform, devolution, new burdens, and GDPR breach risks.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carol Pilson</t>
+          <t>Horizon scanning, financial planning, and responding to consultations</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Implement horizon scanning, staff training, professional networking, and respond to government consultations to proactively manage legislative changes and ensure GDPR compliance.</t>
-        </is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
         <v>6</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Brexit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brexit-related uncertainty and potential legislative, funding, and policy changes may adversely affect the Council's ability to provide services.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Peter Catchpole / Carol Pilson</t>
+          <t>Horizon scanning by Legal Services / CMT / Heads of Service - Financial &amp; workforce planning - Membership of professional and Local Govt bodies aids horizon scanning - Management of change approach to mitigate against significant impact to the organisation and its staff - Detailed project plans to manage implementation of changes</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Conduct horizon scanning, financial and workforce planning, and manage change through detailed project plans to implement necessary adjustments.</t>
-        </is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
         <v>6</v>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>Funding changes make Council unsustainable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Changes to government funding systems and economic conditions could make the Council financially unsustainable.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Peter Catchpole</t>
+          <t>S151/ Chief Finance Officer - Financial Regulations &amp; Standing Orders - Appropriately trained staff - MTFS - Professional economic forecasts - Community consultation on service priorities - Our CSR programme - Political decisions linked to budget strategies - CMT efficiency planning - Efficiency Plan and CSR plan. - Executive steer of service /capital priorities. - Review fees /changes. - Reserves - Financial Mgt System - Budget monitoring.</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
         <v>6</v>
       </c>
-      <c r="H11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Implement and monitor the Commercialisation and Investment Strategy, while actively participating in national working groups to lobby for a stable future funding system.</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>7</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>Fraud and error committed against the Council</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fraud and error committed against the Council by internal or external threats, leading to financial loss, reputational harm, and additional costs.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Peter Catchpole / Carol Pilson</t>
+          <t>Anti-fraud &amp; corruption policy/ strategy, Financial Regulations, Codes of conduct, Appropriately trained staff, Appropriate culture and risk awareness, Segregation of duties, Supported financial management system, Budget monitoring regime, Internal Audit review of systems and controls, Bribery &amp; corruption / fraud risk assessments, Indemnity insurance, Whistle-blowing procedure, Annual Governance Statement, ARP fraud resource, National Fraud Initiative</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Implement and enforce anti-fraud policies, conduct regular fraud risk assessments, and provide ongoing fraud awareness training for all staff.</t>
-        </is>
+      <c r="J12" t="n">
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>Failure of Governance in major partners or in the Council as a result of partnership working</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Failure of governance in major partners or the Council due to partnership working, leading to unachieved priorities and poor performance.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Carol Pilson / Peter Catchpole</t>
+          <t>FSP, Fenland Public Service Board, Cabinet and O&amp;S, bi-annual stakeholder events ensure accountability - ARP Joint Committee and Operational Improvement Board, Cabinet, O&amp;S, joint risk registers - CNC Joint Members Board, Cabinet plus O&amp;S - Shared Planning Board, Cabinet plus Overview and Scrutiny, joint performance indicators - Project plans / perf’ monitoring shared risk registers - PCCA Membership</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
-        <v>8</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Ensure governance models are correctly followed, support Members in partnership governance, and conduct internal audits of partnership arrangements.</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>Failure to achieve required savings targets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Failure to achieve required savings targets results in greater than budgeted costs and potential risk of Council not being able to set a balanced budget.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cmt</t>
+          <t>Heightened analysis of budgets and services by CMT, implement Service Transformation, implement Procurement Strategy, Corporate plan, pursue action to increase income streams, Performance Management Framework, budget and performance monitoring, robust Workforce planning, Project Management processes</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Implement robust budget and performance monitoring, service transformation projects, and a commercialisation strategy to control costs and increase income streams.</t>
-        </is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>Capital funding strategy failure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Capital funding strategy failure leading to financial shortfalls and increased burden on the Council.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Peter Catchpole</t>
+          <t>Asset mgt plan - Asset disposal linked to capital programme - Corporate Asset Team - CMT monitoring of capital receipts/effect on capital prog’ - Regular Cabinet review of the capital prog’ , member with responsibility for assets - Additional funding opp’s identified and pursued where possible - Project lead monitors site valuations linked to econ’ dev’ proposals. - Marketing and identification of potential land purchasers, flexibility of planning guidance aligned to market needs - Continued consultation with econ ptners</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
         <v>8</v>
@@ -1304,52 +1304,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Implement asset management plan, disposal strategy, and regular high-level monitoring of capital receipts and funding opportunities.</t>
-        </is>
+      <c r="J15" t="n">
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
         <v>6</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>Poor communications with stakeholders</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poor communication with stakeholders and staff leads to poorly informed direction of resources and lack of support for change.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stakeholder</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carol Pilson</t>
+          <t>Internal and external regular publications, staff meetings, and consultation forums</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1363,115 +1363,115 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Implement regular internal/external publications, staff meetings, stakeholder networks, and coordinated communication programs.</t>
-        </is>
+      <c r="J16" t="n">
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>Commercial uncertainties associated with decisions taken as part of the Council’s Commercial and Investment Strategy.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Commercial uncertainties associated with decisions taken as part of the Council's Commercial and Investment Strategy.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cmt</t>
+          <t>Robust oversight and governance arrangements, expert professional advice, robust budget management, thorough project management and business cases process.</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Implement robust oversight, governance arrangements, and expert professional advice to manage commercial uncertainties.</t>
-        </is>
+      <c r="J17" t="n">
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>Failure of external investment institutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Failure of external investment institutions affecting availability of funds or return on investment, reducing cash flow and resource availability.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Peter Catchpole</t>
+          <t>Policy for maximum investment/borrowing levels limits liability - Credit ratings - Financial management - Reserves - Insurance - Medium Term Financial Strategy - Treasury Management Strategy</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>8</v>
@@ -1481,174 +1481,174 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Implement and maintain an effective Treasury Management strategy with robust auditing of processes and policies.</t>
-        </is>
+      <c r="J18" t="n">
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
         <v>6</v>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>Insufficient staff to provide Council services Insufficient leadership and/or management capacity to deliver Council priorities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Insufficient staff and leadership capacity to deliver Council services and priorities, leading to poor service standards, disruption, and potential legal challenges.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cmt</t>
+          <t>Learning &amp; Development framework / Training - Working environment /culture - Staff Committee - MTSP - Flexible working - Established suite of people policies &amp; Procedures - Business continuity plans - Management training - 121s /Springboard staff development and appraisals - Service planning process - Access to interim staff via frameworks - Effective sickness management - Effective Governance structures</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Ensure all services have effective Workforce Plans incorporated into Service Plans and implement effective succession planning.</t>
-        </is>
+      <c r="J19" t="n">
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>Lack of access to Council premises prevents services being delivered</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lack of access to Council premises prevents services from being delivered, causing service disruption.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Peter Catchpole</t>
+          <t>Alarm and security systems, Fire drills, Business continuity plans, Emergency planning network, ICT disaster recovery and offsite testing, Relocation procedures - critical and support services, Geographically distributed sites, Remote working, Statutory building inspection and checks, Corporate Business Continuity Plans</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Regularly test and update business continuity and emergency plans, including remote working capabilities.</t>
-        </is>
+      <c r="J20" t="n">
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>Over-run of major Council projects in time or cost</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Over-run of major Council projects in time or cost leading to failure to achieve project aims and reputational damage.</t>
+          <t>Construction / Operation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cmt</t>
+          <t>Project Management methodology - Contract Standing Orders &amp; Financial Regulations - Service plans - Budgetary control - Management and Portfolio Holder oversight</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
         <v>8</v>
@@ -1658,1200 +1658,1176 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Implement robust project management methodology and maintain effective risk registers for all projects.</t>
-        </is>
+      <c r="J21" t="n">
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
         <v>6</v>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Legislative changes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Legislative changes could impact project compliance and viability.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Legislative changes</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
         <v>4</v>
       </c>
-      <c r="H22" t="n">
-        <v>7</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Monitor regulatory updates and engage legal counsel to assess impacts on project plans.</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Brexit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brexit-related uncertainties affecting project operations and compliance.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Regulations</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Brexit</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Monitor Brexit developments and update project compliance plans accordingly.</t>
-        </is>
+      <c r="J23" t="n">
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Failure of contractors and suppliers working on the Council’s behalf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contractors and suppliers working on the Council’s behalf may fail to deliver.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Procurement Manager</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Ensure robust contractor and supplier management processes</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
         <v>4</v>
       </c>
-      <c r="H24" t="n">
-        <v>7</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>The Project Manager must implement robust contract monitoring and enforce service level agreements.</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>5</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>Failure of IT systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Failure of IT systems.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Uaa Lead</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Failure of IT systems</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Implement and regularly test system redundancy and data backup procedures.</t>
-        </is>
+      <c r="J25" t="n">
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>Insufficient staff to provide Council services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Insufficient staff to provide Council services.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Insufficient staff to provide Council services</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
         <v>4</v>
       </c>
-      <c r="H26" t="n">
-        <v>8</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Develop and implement a recruitment and retention strategy to ensure adequate staffing levels.</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>Breach of ICT security causes loss of service</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A breach of ICT security causes loss of service.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Uaa Lead</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Breach of ICT security causes loss of service</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Implement enhanced cybersecurity protocols and regular security audits.</t>
-        </is>
+      <c r="J27" t="n">
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>Lack of access to Council premises prevents services being delivered</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lack of access to Council premises prevents services from being delivered.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Develop and implement a robust business continuity plan with remote service delivery options.</t>
-        </is>
+      <c r="J28" t="n">
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>Funding changes make Council unsustainable</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Changes in funding could render the Council financially unsustainable.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Develop and maintain a diversified funding strategy and robust financial contingency plans.</t>
-        </is>
+      <c r="J29" t="n">
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>The Councils ability to cope with a natural disaster</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The Council's ability to cope with a natural disaster is insufficient.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
         <v>4</v>
       </c>
-      <c r="H30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Develop and test a comprehensive business continuity and disaster recovery plan.</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6</v>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>Major health and safety incident</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A major health and safety incident occurring on the project.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Construction Manager</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Major health and safety incident</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Implement and enforce a comprehensive site safety plan with regular audits and staff training.</t>
-        </is>
+      <c r="J31" t="n">
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>Fraud &amp; error committed against Council</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fraud and error are committed against the Council, leading to financial loss and reputational damage.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Fraud &amp; error committed against Council</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Implement robust financial controls, regular audits, and staff training on fraud prevention and detection procedures.</t>
-        </is>
+      <c r="J32" t="n">
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>Failure of external investment institutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Failure of external investment institutions could disrupt project funding.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Failure of external investment institutions</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
         <v>4</v>
       </c>
-      <c r="H33" t="n">
-        <v>8</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Diversify funding sources and conduct regular financial health checks on investment partners.</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6</v>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>Failure of Governance in major partners/the Council as a result of partnership working</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Failure of governance in major partners or the Council due to partnership working.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
         <v>4</v>
       </c>
-      <c r="H34" t="n">
-        <v>8</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Establish and regularly review clear governance frameworks and communication protocols with all partners.</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6</v>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>Failure to achieve required savings targets</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Failure to achieve required savings targets.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Failure to achieve required savings targets</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Implement strict budget monitoring and regular financial reviews to track savings progress.</t>
-        </is>
+      <c r="J35" t="n">
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>Over-run of major Council projects in time or cost</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Major Council projects may over-run in time or cost.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>5</v>
       </c>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Implement rigorous project monitoring, milestone tracking, and contingency planning.</t>
-        </is>
+      <c r="J36" t="n">
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>Service provision affected by organisational change</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Service provision is affected by organisational change.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Develop and implement a business continuity plan to maintain service levels during organisational transitions.</t>
-        </is>
+      <c r="J37" t="n">
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>Political changes in national priorities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Political changes in national priorities could affect project support or funding.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Regulations</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Political changes in national priorities</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
         <v>4</v>
       </c>
-      <c r="H38" t="n">
-        <v>7</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Monitor political developments and engage with relevant government bodies to understand and adapt to changing priorities.</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>2</v>
-      </c>
-      <c r="L38" t="n">
-        <v>5</v>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>Capital funding strategy failure</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Failure of the capital funding strategy.</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Capital funding strategy failure</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="n">
-        <v>9</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Develop and regularly review a robust, diversified funding plan with clear contingency measures.</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>7</v>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>Poor communications with stakeholders</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poor communications with stakeholders.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stakeholder</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Poor communications with stakeholders</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Establish and maintain a formal stakeholder communication plan with regular updates.</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" t="n">
-        <v>4</v>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>Failure of Commercialisation &amp; Investment Strategy.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>The project faces a risk due to the potential failure of its Commercialisation &amp; Investment Strategy.</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Failure of Commercialisation &amp; Investment Strategy.</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>5</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Develop and implement a robust, reviewed commercialisation and investment plan with clear milestones.</t>
-        </is>
+      <c r="J41" t="n">
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
-      </c>
-      <c r="L41" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
